--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T05:20:25+00:00</t>
+    <t>2026-09-28T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:16:57+00:00</t>
+    <t>2026-09-28T10:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:26:56+00:00</t>
+    <t>2026-09-28T11:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:29:30+00:00</t>
+    <t>2026-09-28T12:11:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -461,6 +461,26 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>MedicationRequest.extension:kontext</t>
+  </si>
+  <si>
+    <t>kontext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-behandlungs-kontext}
+</t>
+  </si>
+  <si>
+    <t>Kontext</t>
+  </si>
+  <si>
+    <t>Dieses Feld soll dazu dienen, neben der Therapieintention einzelnen Behandlungsschritten weiteren Kontext zu geben.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:changeType</t>
   </si>
   <si>
@@ -475,10 +495,6 @@
   </si>
   <si>
     <t>Änderungstyp nach EnLiST — new, modified oder same.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -1866,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -2982,7 +2998,7 @@
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>91</v>
@@ -3081,48 +3097,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>81</v>
       </c>
@@ -3170,7 +3184,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3179,7 +3193,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -3191,7 +3205,7 @@
         <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>81</v>
@@ -3202,14 +3216,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3222,24 +3236,26 @@
         <v>81</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3287,7 +3303,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3299,30 +3315,30 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3330,31 +3346,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3380,13 +3396,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3404,13 +3420,13 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
@@ -3419,27 +3435,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3447,31 +3463,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3497,13 +3513,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -3521,10 +3537,10 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3536,27 +3552,27 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3564,31 +3580,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3614,13 +3630,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3638,10 +3654,10 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>90</v>
@@ -3653,27 +3669,27 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3684,28 +3700,28 @@
         <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3731,35 +3747,37 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
@@ -3768,31 +3786,29 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>81</v>
       </c>
@@ -3801,7 +3817,7 @@
         <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>91</v>
@@ -3813,16 +3829,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3833,7 +3849,7 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>81</v>
@@ -3848,31 +3864,29 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AC17" s="2"/>
+      <c r="AD17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3890,55 +3904,59 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -3948,7 +3966,7 @@
         <v>81</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>81</v>
@@ -3963,13 +3981,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3987,13 +4005,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4002,16 +4020,16 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4019,10 +4037,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4039,23 +4057,21 @@
         <v>81</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4080,13 +4096,13 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>81</v>
@@ -4104,7 +4120,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4119,16 +4135,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4136,10 +4152,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4156,21 +4172,23 @@
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4219,7 +4237,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4249,7 +4267,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>227</v>
       </c>
@@ -4262,13 +4280,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>81</v>
@@ -4285,9 +4303,7 @@
       <c r="M21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4312,13 +4328,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>233</v>
+        <v>81</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4339,7 +4355,7 @@
         <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>90</v>
@@ -4351,27 +4367,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>238</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4394,16 +4410,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4429,13 +4445,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4453,7 +4469,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4468,27 +4484,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4496,31 +4512,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4570,10 +4586,10 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4585,27 +4601,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4616,7 +4632,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4628,15 +4644,17 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4685,13 +4703,13 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
@@ -4700,27 +4718,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4731,7 +4749,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -4740,16 +4758,16 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4800,13 +4818,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -4815,27 +4833,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4849,7 +4867,7 @@
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
@@ -4858,13 +4876,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4915,7 +4933,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4930,27 +4948,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4970,16 +4988,16 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5030,7 +5048,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5045,27 +5063,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN27" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5079,26 +5097,24 @@
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5123,13 +5139,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>290</v>
+        <v>81</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5147,7 +5163,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5162,16 +5178,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5179,10 +5195,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5202,18 +5218,20 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>181</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5238,13 +5256,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5262,7 +5280,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5277,7 +5295,7 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
@@ -5286,7 +5304,7 @@
         <v>298</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5294,10 +5312,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5308,7 +5326,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5320,7 +5338,7 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>301</v>
@@ -5328,9 +5346,7 @@
       <c r="M30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5355,13 +5371,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5379,13 +5395,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5394,27 +5410,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>310</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5437,16 +5453,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5472,13 +5488,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5496,7 +5512,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5511,27 +5527,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>172</v>
+        <v>312</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5551,18 +5567,20 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5611,7 +5629,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5626,16 +5644,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5643,10 +5661,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5669,7 +5687,7 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>324</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>325</v>
@@ -5726,7 +5744,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5741,13 +5759,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5758,10 +5776,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5784,13 +5802,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5841,7 +5859,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5856,13 +5874,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5873,10 +5891,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5887,7 +5905,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5899,7 +5917,7 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>156</v>
+        <v>333</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>334</v>
@@ -5908,9 +5926,7 @@
         <v>335</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>336</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5958,13 +5974,13 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
@@ -5973,13 +5989,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5990,10 +6006,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6013,21 +6029,21 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6051,13 +6067,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6075,7 +6091,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6090,13 +6106,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6107,10 +6123,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6121,7 +6137,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6133,15 +6149,17 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6166,13 +6184,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6190,13 +6208,13 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
@@ -6205,13 +6223,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6222,10 +6240,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6248,13 +6266,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6305,7 +6323,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6320,13 +6338,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6337,10 +6355,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6363,17 +6381,15 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L39" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>363</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6422,7 +6438,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6437,13 +6453,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6454,10 +6470,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6468,7 +6484,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6480,15 +6496,17 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6537,13 +6555,13 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
@@ -6552,13 +6570,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>369</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6569,10 +6587,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6595,13 +6613,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6652,7 +6670,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6664,16 +6682,16 @@
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6684,21 +6702,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6710,7 +6728,7 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>378</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>379</v>
@@ -6718,9 +6736,7 @@
       <c r="M42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6775,13 +6791,13 @@
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -6790,7 +6806,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6801,14 +6817,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>383</v>
+        <v>154</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6821,10 +6837,10 @@
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>135</v>
@@ -6836,11 +6852,9 @@
         <v>385</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6909,7 +6923,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>133</v>
+        <v>382</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6927,37 +6941,39 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>367</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7005,19 +7021,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7026,7 +7042,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>391</v>
+        <v>133</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7063,15 +7079,17 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7120,7 +7138,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7132,7 +7150,7 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
@@ -7141,7 +7159,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7152,21 +7170,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7178,7 +7196,7 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>378</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>379</v>
@@ -7186,9 +7204,7 @@
       <c r="M46" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7243,13 +7259,13 @@
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7258,7 +7274,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7269,14 +7285,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>383</v>
+        <v>154</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7289,10 +7305,10 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>135</v>
@@ -7304,11 +7320,9 @@
         <v>385</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7377,7 +7391,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>133</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7388,42 +7402,46 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>396</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7471,19 +7489,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7492,7 +7510,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>399</v>
+        <v>133</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7644,13 +7662,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7722,7 +7740,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7733,10 +7751,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7759,20 +7777,16 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="O51" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7820,7 +7834,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7838,10 +7852,10 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -7852,10 +7866,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7878,18 +7892,20 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -7937,7 +7953,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7955,24 +7971,24 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7995,15 +8011,17 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8052,7 +8070,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8070,24 +8088,24 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8113,14 +8131,12 @@
         <v>401</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8169,7 +8185,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8187,24 +8203,24 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8227,15 +8243,17 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8284,7 +8302,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8302,13 +8320,13 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8342,13 +8360,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>367</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8417,13 +8435,13 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>445</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8457,13 +8475,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>448</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8514,7 +8532,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8526,16 +8544,16 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>377</v>
+        <v>450</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8546,21 +8564,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8572,7 +8590,7 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>378</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>379</v>
@@ -8580,9 +8598,7 @@
       <c r="M58" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8637,13 +8653,13 @@
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -8652,7 +8668,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8663,14 +8679,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>383</v>
+        <v>154</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8683,10 +8699,10 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>135</v>
@@ -8698,11 +8714,9 @@
         <v>385</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8771,7 +8785,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>133</v>
+        <v>382</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8782,44 +8796,46 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>450</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>452</v>
+        <v>390</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8843,13 +8859,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8867,42 +8883,42 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>456</v>
+        <v>133</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>457</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8910,7 +8926,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>90</v>
@@ -8925,15 +8941,17 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>176</v>
+        <v>455</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8958,13 +8976,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8982,10 +9000,10 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>90</v>
@@ -9000,24 +9018,24 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9040,13 +9058,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>467</v>
+        <v>181</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9073,13 +9091,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>81</v>
+        <v>466</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9097,7 +9115,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9112,38 +9130,38 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9155,17 +9173,15 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9214,13 +9230,13 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
@@ -9229,13 +9245,13 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9246,14 +9262,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9272,16 +9288,16 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9331,7 +9347,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9346,23 +9362,140 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="B65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO64" t="s" s="2">
+      <c r="L65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO64">
+  <autoFilter ref="A1:AO65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9372,7 +9505,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:11:39+00:00</t>
+    <t>2026-09-28T20:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T20:57:11+00:00</t>
+    <t>2026-09-28T21:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:01:12+00:00</t>
+    <t>2026-09-30T11:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:29:35+00:00</t>
+    <t>2026-10-01T05:55:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/ci-build/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
